--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202608/Category_P&L_20260806.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202608/Category_P&L_20260806.xlsx
@@ -44917,7 +44917,7 @@
         <v>46233</v>
       </c>
       <c r="B1172">
-        <v>85859219.67</v>
+        <v>87859219.67</v>
       </c>
       <c r="C1172">
         <v>2560679.54</v>
@@ -44955,19 +44955,19 @@
         <v>46234</v>
       </c>
       <c r="B1173">
-        <v>86263492.97</v>
+        <v>88263665.98999999</v>
       </c>
       <c r="C1173">
         <v>409896.17</v>
       </c>
       <c r="D1173">
-        <v>0.004774</v>
+        <v>0.004665</v>
       </c>
       <c r="E1173">
         <v>9174.1</v>
       </c>
       <c r="F1173">
-        <v>0.000107</v>
+        <v>0.000104</v>
       </c>
       <c r="G1173">
         <v>-2</v>
@@ -44993,19 +44993,19 @@
         <v>46237</v>
       </c>
       <c r="B1174">
-        <v>87113767.19</v>
+        <v>89113874.08</v>
       </c>
       <c r="C1174">
-        <v>943725.96</v>
+        <v>943140.77</v>
       </c>
       <c r="D1174">
-        <v>0.01094</v>
+        <v>0.010685</v>
       </c>
       <c r="E1174">
         <v>-133023.1</v>
       </c>
       <c r="F1174">
-        <v>-0.001542</v>
+        <v>-0.001507</v>
       </c>
       <c r="G1174">
         <v>112</v>
@@ -45031,19 +45031,19 @@
         <v>46238</v>
       </c>
       <c r="B1175">
-        <v>91262886.70999999</v>
+        <v>93267004.43000001</v>
       </c>
       <c r="C1175">
-        <v>4163918.7</v>
+        <v>4167557.29</v>
       </c>
       <c r="D1175">
-        <v>0.047799</v>
+        <v>0.046767</v>
       </c>
       <c r="E1175">
         <v>4612.7</v>
       </c>
       <c r="F1175">
-        <v>5.3E-05</v>
+        <v>5.2E-05</v>
       </c>
       <c r="G1175">
         <v>-156</v>
@@ -45069,19 +45069,19 @@
         <v>46239</v>
       </c>
       <c r="B1176">
-        <v>90306025.06999999</v>
+        <v>92301723.41</v>
       </c>
       <c r="C1176">
-        <v>-945526.08</v>
+        <v>-954071.02</v>
       </c>
       <c r="D1176">
-        <v>-0.01036</v>
+        <v>-0.010229</v>
       </c>
       <c r="E1176">
         <v>9168.700000000001</v>
       </c>
       <c r="F1176">
-        <v>0.0001</v>
+        <v>9.8E-05</v>
       </c>
       <c r="G1176">
         <v>-110</v>
@@ -45107,19 +45107,19 @@
         <v>46240</v>
       </c>
       <c r="B1177">
-        <v>90022498.70999999</v>
+        <v>92036435.27</v>
       </c>
       <c r="C1177">
-        <v>-268398.94</v>
+        <v>-250242.74</v>
       </c>
       <c r="D1177">
-        <v>-0.002972</v>
+        <v>-0.002711</v>
       </c>
       <c r="E1177">
         <v>103113.02</v>
       </c>
       <c r="F1177">
-        <v>0.001142</v>
+        <v>0.001117</v>
       </c>
       <c r="G1177">
         <v>-13</v>
